--- a/data/trans_orig/Q70-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q70-Estudios-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7,76</t>
+          <t>5,97</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>8,15</t>
+          <t>7,93</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,91</t>
+          <t>6,65</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,12; 3,96</t>
+          <t>1,11; 4,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,99; 4,3</t>
+          <t>0,9; 4,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,18; 5,37</t>
+          <t>1,18; 5,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,36; 17,54</t>
+          <t>2,7; 16,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,52</t>
+          <t>0,44; 1,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,36; 4,3</t>
+          <t>0,34; 4,48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,16; 3,54</t>
+          <t>0,15; 3,44</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,87; 21,0</t>
+          <t>2,96; 20,37</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,02; 3,15</t>
+          <t>1,07; 3,76</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,9; 3,29</t>
+          <t>0,88; 3,15</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,77</t>
+          <t>1,01; 3,62</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,33; 15,28</t>
+          <t>3,57; 11,95</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,93</t>
+          <t>6,69</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8,69</t>
+          <t>9,28</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7,05</t>
+          <t>7,79</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,45</t>
+          <t>1,01; 2,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,82</t>
+          <t>0,96; 2,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,5; 4,16</t>
+          <t>1,53; 4,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,59; 8,05</t>
+          <t>5,09; 8,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,66; 5,51</t>
+          <t>1,61; 5,07</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,39; 5,64</t>
+          <t>1,39; 5,49</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 4,02</t>
+          <t>1,16; 4,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,42; 11,12</t>
+          <t>7,46; 11,49</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,35; 2,85</t>
+          <t>1,35; 2,86</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,38; 3,26</t>
+          <t>1,34; 3,08</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,57; 3,45</t>
+          <t>1,5; 3,42</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,25; 8,72</t>
+          <t>6,61; 9,29</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,66</t>
+          <t>5,62</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6,91</t>
+          <t>6,73</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,28</t>
+          <t>6,17</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,46; 0,98</t>
+          <t>0,48; 1,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 7,86</t>
+          <t>0,55; 8,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,65</t>
+          <t>0,52; 2,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,41; 12,2</t>
+          <t>3,41; 12,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 3,64</t>
+          <t>0,47; 3,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,45</t>
+          <t>0,42; 1,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,26; 5,44</t>
+          <t>1,31; 5,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,03; 9,75</t>
+          <t>4,82; 9,45</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,23</t>
+          <t>0,56; 2,21</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,61; 4,24</t>
+          <t>0,61; 3,9</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,07; 3,09</t>
+          <t>1,07; 3,03</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,68; 9,47</t>
+          <t>4,69; 9,58</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,0</t>
+          <t>6,36</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>8,13</t>
+          <t>8,4</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,91</t>
+          <t>7,25</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,05; 2,05</t>
+          <t>1,08; 2,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,05; 2,92</t>
+          <t>1,13; 2,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,41; 3,38</t>
+          <t>1,42; 3,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,29; 7,84</t>
+          <t>5,08; 8,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,23; 3,29</t>
+          <t>1,26; 3,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,15; 3,76</t>
+          <t>1,15; 3,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,41</t>
+          <t>1,42; 3,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,62; 9,95</t>
+          <t>7,03; 10,11</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,21; 2,15</t>
+          <t>1,23; 2,19</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,26; 2,65</t>
+          <t>1,25; 2,68</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,56; 2,91</t>
+          <t>1,54; 2,76</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,55; 8,27</t>
+          <t>6,23; 8,54</t>
         </is>
       </c>
     </row>
